--- a/data/Original datasets/CBRA MOD.xlsx
+++ b/data/Original datasets/CBRA MOD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\PHD_Projects\MechanisticAI\MechanisticsAI_julia\data\Original datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F921EC52-6042-44FA-980D-6FCB3A9D8B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6E2DEA-6F8C-4C70-B416-0167F1BE7EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-4815" windowWidth="18240" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4522,6 +4522,7 @@
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
